--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD1E095-10CE-42D9-B139-2ED3A7D60810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75BE017-FA6B-4A72-8653-A08C03C2B413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983</t>
+    <t>01/01/1983 00:00:00</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>10/09/2024 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>ABDRAMAN IBRAHIM</t>
@@ -85,7 +85,7 @@
     <t>M</t>
   </si>
   <si>
-    <t>01/09/2025</t>
+    <t>01/09/2025 00:00:00</t>
   </si>
   <si>
     <t>ABIA</t>
@@ -94,13 +94,13 @@
     <t>Flore</t>
   </si>
   <si>
-    <t>19/08/2000</t>
+    <t>19/08/2000 00:00:00</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>23/09/2025</t>
+    <t>23/09/2025 00:00:00</t>
   </si>
   <si>
     <t>AVAGYAN</t>
@@ -109,13 +109,13 @@
     <t>Karen</t>
   </si>
   <si>
-    <t>04/10/1980</t>
+    <t>04/10/1980 00:00:00</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>10/12/2024</t>
+    <t>10/12/2024 00:00:00</t>
   </si>
   <si>
     <t>BURDULI</t>
@@ -124,13 +124,13 @@
     <t>Sopio</t>
   </si>
   <si>
-    <t>02/04/1997</t>
+    <t>02/04/1997 00:00:00</t>
   </si>
   <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>11/10/2023</t>
+    <t>11/10/2023 00:00:00</t>
   </si>
   <si>
     <t>HIRPA</t>
@@ -142,7 +142,7 @@
     <t>Éthiopie</t>
   </si>
   <si>
-    <t>16/09/2025</t>
+    <t>16/09/2025 00:00:00</t>
   </si>
   <si>
     <t>JISHKARIANI</t>
@@ -151,10 +151,10 @@
     <t>Nino</t>
   </si>
   <si>
-    <t>11/02/1980</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
+    <t>11/02/1980 00:00:00</t>
+  </si>
+  <si>
+    <t>06/11/2025 00:00:00</t>
   </si>
   <si>
     <t>KATCHATRYAN</t>
@@ -163,19 +163,19 @@
     <t>Anna</t>
   </si>
   <si>
-    <t>20/05/1980</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
+    <t>20/05/1980 00:00:00</t>
+  </si>
+  <si>
+    <t>07/11/2025 00:00:00</t>
   </si>
   <si>
     <t>Mariam</t>
   </si>
   <si>
-    <t>26/08/1986</t>
-  </si>
-  <si>
-    <t>06/10/2022</t>
+    <t>26/08/1986 00:00:00</t>
+  </si>
+  <si>
+    <t>06/10/2022 00:00:00</t>
   </si>
   <si>
     <t>MUGENI</t>
@@ -184,10 +184,10 @@
     <t>Chantal</t>
   </si>
   <si>
-    <t>31/12/1996</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
+    <t>31/12/1996 00:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MUSTAFAYEV</t>
@@ -196,7 +196,7 @@
     <t>Elshan</t>
   </si>
   <si>
-    <t>17/07/1978</t>
+    <t>17/07/1978 00:00:00</t>
   </si>
   <si>
     <t>Azerbaïdjan</t>
@@ -208,13 +208,13 @@
     <t>Wuod</t>
   </si>
   <si>
-    <t>01/06/1970</t>
+    <t>01/06/1970 00:00:00</t>
   </si>
   <si>
     <t>Irak</t>
   </si>
   <si>
-    <t>15/11/2022</t>
+    <t>15/11/2022 00:00:00</t>
   </si>
   <si>
     <t>PETUKHOVA</t>
@@ -223,13 +223,13 @@
     <t>Mariila</t>
   </si>
   <si>
-    <t>05/11/1951</t>
+    <t>05/11/1951 00:00:00</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>10/09/2025</t>
+    <t>10/09/2025 00:00:00</t>
   </si>
   <si>
     <t>RAHHAL</t>
@@ -238,7 +238,7 @@
     <t>Abdelkader</t>
   </si>
   <si>
-    <t>03/07/1984</t>
+    <t>03/07/1984 00:00:00</t>
   </si>
   <si>
     <t>Algérie</t>
@@ -250,10 +250,10 @@
     <t>Kajol</t>
   </si>
   <si>
-    <t>08/07/2004</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
+    <t>08/07/2004 00:00:00</t>
+  </si>
+  <si>
+    <t>03/09/2025 00:00:00</t>
   </si>
   <si>
     <t>SHOTSHA</t>
@@ -262,7 +262,7 @@
     <t>M'wemwe</t>
   </si>
   <si>
-    <t>05/05/1981</t>
+    <t>05/05/1981 00:00:00</t>
   </si>
   <si>
     <t>TOLA</t>
@@ -271,7 +271,7 @@
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004</t>
+    <t>27/08/2004 00:00:00</t>
   </si>
   <si>
     <t>TSAGAREISHVILI</t>
@@ -280,10 +280,10 @@
     <t>Gela</t>
   </si>
   <si>
-    <t>05/11/1984</t>
-  </si>
-  <si>
-    <t>28/05/2024</t>
+    <t>05/11/1984 00:00:00</t>
+  </si>
+  <si>
+    <t>28/05/2024 00:00:00</t>
   </si>
   <si>
     <t>WRETA</t>
@@ -292,10 +292,10 @@
     <t>Abeje</t>
   </si>
   <si>
-    <t>05/05/1997</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
+    <t>05/05/1997 00:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2025 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75BE017-FA6B-4A72-8653-A08C03C2B413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293FCBF-E287-4F47-9AC4-FA16602CAE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983 00:00:00</t>
+    <t>01/01/1983</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>ABDRAMAN IBRAHIM</t>
@@ -85,7 +85,7 @@
     <t>M</t>
   </si>
   <si>
-    <t>01/09/2025 00:00:00</t>
+    <t>01/09/2025</t>
   </si>
   <si>
     <t>ABIA</t>
@@ -94,13 +94,13 @@
     <t>Flore</t>
   </si>
   <si>
-    <t>19/08/2000 00:00:00</t>
+    <t>19/08/2000</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>23/09/2025 00:00:00</t>
+    <t>23/09/2025</t>
   </si>
   <si>
     <t>AVAGYAN</t>
@@ -109,13 +109,13 @@
     <t>Karen</t>
   </si>
   <si>
-    <t>04/10/1980 00:00:00</t>
+    <t>04/10/1980</t>
   </si>
   <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>10/12/2024 00:00:00</t>
+    <t>10/12/2024</t>
   </si>
   <si>
     <t>BURDULI</t>
@@ -124,13 +124,13 @@
     <t>Sopio</t>
   </si>
   <si>
-    <t>02/04/1997 00:00:00</t>
+    <t>02/04/1997</t>
   </si>
   <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>11/10/2023 00:00:00</t>
+    <t>11/10/2023</t>
   </si>
   <si>
     <t>HIRPA</t>
@@ -142,7 +142,7 @@
     <t>Éthiopie</t>
   </si>
   <si>
-    <t>16/09/2025 00:00:00</t>
+    <t>16/09/2025</t>
   </si>
   <si>
     <t>JISHKARIANI</t>
@@ -151,10 +151,10 @@
     <t>Nino</t>
   </si>
   <si>
-    <t>11/02/1980 00:00:00</t>
-  </si>
-  <si>
-    <t>06/11/2025 00:00:00</t>
+    <t>11/02/1980</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
   </si>
   <si>
     <t>KATCHATRYAN</t>
@@ -163,19 +163,19 @@
     <t>Anna</t>
   </si>
   <si>
-    <t>20/05/1980 00:00:00</t>
-  </si>
-  <si>
-    <t>07/11/2025 00:00:00</t>
+    <t>20/05/1980</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
   </si>
   <si>
     <t>Mariam</t>
   </si>
   <si>
-    <t>26/08/1986 00:00:00</t>
-  </si>
-  <si>
-    <t>06/10/2022 00:00:00</t>
+    <t>26/08/1986</t>
+  </si>
+  <si>
+    <t>06/10/2022</t>
   </si>
   <si>
     <t>MUGENI</t>
@@ -184,10 +184,10 @@
     <t>Chantal</t>
   </si>
   <si>
-    <t>31/12/1996 00:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2025 00:00:00</t>
+    <t>31/12/1996</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>MUSTAFAYEV</t>
@@ -196,7 +196,7 @@
     <t>Elshan</t>
   </si>
   <si>
-    <t>17/07/1978 00:00:00</t>
+    <t>17/07/1978</t>
   </si>
   <si>
     <t>Azerbaïdjan</t>
@@ -208,13 +208,13 @@
     <t>Wuod</t>
   </si>
   <si>
-    <t>01/06/1970 00:00:00</t>
+    <t>01/06/1970</t>
   </si>
   <si>
     <t>Irak</t>
   </si>
   <si>
-    <t>15/11/2022 00:00:00</t>
+    <t>15/11/2022</t>
   </si>
   <si>
     <t>PETUKHOVA</t>
@@ -223,13 +223,13 @@
     <t>Mariila</t>
   </si>
   <si>
-    <t>05/11/1951 00:00:00</t>
+    <t>05/11/1951</t>
   </si>
   <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>10/09/2025 00:00:00</t>
+    <t>10/09/2025</t>
   </si>
   <si>
     <t>RAHHAL</t>
@@ -238,7 +238,7 @@
     <t>Abdelkader</t>
   </si>
   <si>
-    <t>03/07/1984 00:00:00</t>
+    <t>03/07/1984</t>
   </si>
   <si>
     <t>Algérie</t>
@@ -250,10 +250,10 @@
     <t>Kajol</t>
   </si>
   <si>
-    <t>08/07/2004 00:00:00</t>
-  </si>
-  <si>
-    <t>03/09/2025 00:00:00</t>
+    <t>08/07/2004</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
   </si>
   <si>
     <t>SHOTSHA</t>
@@ -262,7 +262,7 @@
     <t>M'wemwe</t>
   </si>
   <si>
-    <t>05/05/1981 00:00:00</t>
+    <t>05/05/1981</t>
   </si>
   <si>
     <t>TOLA</t>
@@ -271,7 +271,7 @@
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004 00:00:00</t>
+    <t>27/08/2004</t>
   </si>
   <si>
     <t>TSAGAREISHVILI</t>
@@ -280,10 +280,10 @@
     <t>Gela</t>
   </si>
   <si>
-    <t>05/11/1984 00:00:00</t>
-  </si>
-  <si>
-    <t>28/05/2024 00:00:00</t>
+    <t>05/11/1984</t>
+  </si>
+  <si>
+    <t>28/05/2024</t>
   </si>
   <si>
     <t>WRETA</t>
@@ -292,10 +292,10 @@
     <t>Abeje</t>
   </si>
   <si>
-    <t>05/05/1997 00:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2025 00:00:00</t>
+    <t>05/05/1997</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293FCBF-E287-4F47-9AC4-FA16602CAE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80B3715-27C1-44C0-9FA4-D2AF17BCA114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80B3715-27C1-44C0-9FA4-D2AF17BCA114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1820EE3B-63E0-43EA-94F4-FEC369065FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1820EE3B-63E0-43EA-94F4-FEC369065FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D965129-C586-4A08-9634-C6B3CE03EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D965129-C586-4A08-9634-C6B3CE03EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BE9D1A-7C59-4EF7-8476-53A8DC29D6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BE9D1A-7C59-4EF7-8476-53A8DC29D6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C8BB42-CECA-44B5-A2F5-E5A99F87A512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C8BB42-CECA-44B5-A2F5-E5A99F87A512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64B91E5-12EB-468D-B48A-3A003EE063C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
